--- a/results/walkforward/walk_forward_SPYG.xlsx
+++ b/results/walkforward/walk_forward_SPYG.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="108" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="135" uniqueCount="19">
   <si>
     <t>Ticker</t>
   </si>

--- a/results/walkforward/walk_forward_SPYG.xlsx
+++ b/results/walkforward/walk_forward_SPYG.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="135" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="181" uniqueCount="48">
   <si>
     <t>Ticker</t>
   </si>
@@ -70,6 +70,93 @@
   </si>
   <si>
     <t>SharpeImprovement</t>
+  </si>
+  <si>
+    <t>BaselineReturnPct</t>
+  </si>
+  <si>
+    <t>ExposureReturnPct</t>
+  </si>
+  <si>
+    <t>BaselineMaxDrawdownPct</t>
+  </si>
+  <si>
+    <t>ExposureMaxDrawdownPct</t>
+  </si>
+  <si>
+    <t>BaselineSharpe</t>
+  </si>
+  <si>
+    <t>ExposureSharpe</t>
+  </si>
+  <si>
+    <t>BuyHoldBuyCount</t>
+  </si>
+  <si>
+    <t>BaselineBuyCount</t>
+  </si>
+  <si>
+    <t>ExposureBuyCount</t>
+  </si>
+  <si>
+    <t>BuyHoldSellCount</t>
+  </si>
+  <si>
+    <t>BaselineSellCount</t>
+  </si>
+  <si>
+    <t>ExposureSellCount</t>
+  </si>
+  <si>
+    <t>BuyHoldTradeCount</t>
+  </si>
+  <si>
+    <t>BaselineTradeCount</t>
+  </si>
+  <si>
+    <t>ExposureTradeCount</t>
+  </si>
+  <si>
+    <t>BuyHoldTimeInMarketPct</t>
+  </si>
+  <si>
+    <t>BaselineTimeInMarketPct</t>
+  </si>
+  <si>
+    <t>ExposureTimeInMarketPct</t>
+  </si>
+  <si>
+    <t>ExposureAveragePct</t>
+  </si>
+  <si>
+    <t>ExposureTurnoverTotal</t>
+  </si>
+  <si>
+    <t>BuyHoldExcessReturnPct</t>
+  </si>
+  <si>
+    <t>BaselineExcessReturnPct</t>
+  </si>
+  <si>
+    <t>ExposureExcessReturnPct</t>
+  </si>
+  <si>
+    <t>BuyHoldDrawdownImprovementPct</t>
+  </si>
+  <si>
+    <t>BaselineDrawdownImprovementPct</t>
+  </si>
+  <si>
+    <t>ExposureDrawdownImprovementPct</t>
+  </si>
+  <si>
+    <t>BuyHoldSharpeImprovement</t>
+  </si>
+  <si>
+    <t>BaselineSharpeImprovement</t>
+  </si>
+  <si>
+    <t>ExposureSharpeImprovement</t>
   </si>
 </sst>
 </file>
@@ -115,7 +202,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:AK10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.83984375" customWidth="true"/>
@@ -123,19 +210,38 @@
     <col min="3" max="3" width="15.5234375" customWidth="true"/>
     <col min="4" max="4" width="15.5234375" customWidth="true"/>
     <col min="5" max="5" width="15.5234375" customWidth="true"/>
-    <col min="6" max="6" width="15.41796875" customWidth="true"/>
-    <col min="7" max="7" width="15.5234375" customWidth="true"/>
-    <col min="8" max="8" width="22.20703125" customWidth="true"/>
+    <col min="6" max="6" width="15.5234375" customWidth="true"/>
+    <col min="7" max="7" width="15.3671875" customWidth="true"/>
+    <col min="8" max="8" width="16.1015625" customWidth="true"/>
     <col min="9" max="9" width="22.3125" customWidth="true"/>
-    <col min="10" max="10" width="13.578125" customWidth="true"/>
-    <col min="11" max="11" width="13.578125" customWidth="true"/>
-    <col min="12" max="12" width="8.7890625" customWidth="true"/>
-    <col min="13" max="13" width="8.5234375" customWidth="true"/>
-    <col min="14" max="14" width="10.3671875" customWidth="true"/>
-    <col min="15" max="15" width="14.734375" customWidth="true"/>
-    <col min="16" max="16" width="13.9453125" customWidth="true"/>
-    <col min="17" max="17" width="22.99609375" customWidth="true"/>
-    <col min="18" max="18" width="17.3671875" customWidth="true"/>
+    <col min="10" max="10" width="22.15625" customWidth="true"/>
+    <col min="11" max="11" width="22.89453125" customWidth="true"/>
+    <col min="12" max="12" width="13.578125" customWidth="true"/>
+    <col min="13" max="13" width="13.578125" customWidth="true"/>
+    <col min="14" max="14" width="14.15625" customWidth="true"/>
+    <col min="15" max="15" width="15.41796875" customWidth="true"/>
+    <col min="16" max="16" width="15.26171875" customWidth="true"/>
+    <col min="17" max="17" width="16" customWidth="true"/>
+    <col min="18" max="18" width="15.15625" customWidth="true"/>
+    <col min="19" max="19" width="15" customWidth="true"/>
+    <col min="20" max="20" width="15.734375" customWidth="true"/>
+    <col min="21" max="21" width="16.99609375" customWidth="true"/>
+    <col min="22" max="22" width="16.83984375" customWidth="true"/>
+    <col min="23" max="23" width="17.578125" customWidth="true"/>
+    <col min="24" max="24" width="21.3671875" customWidth="true"/>
+    <col min="25" max="25" width="21.20703125" customWidth="true"/>
+    <col min="26" max="26" width="21.9453125" customWidth="true"/>
+    <col min="27" max="27" width="17.20703125" customWidth="true"/>
+    <col min="28" max="28" width="19.5234375" customWidth="true"/>
+    <col min="29" max="29" width="20.578125" customWidth="true"/>
+    <col min="30" max="30" width="20.41796875" customWidth="true"/>
+    <col min="31" max="31" width="21.15625" customWidth="true"/>
+    <col min="32" max="32" width="29.62890625" customWidth="true"/>
+    <col min="33" max="33" width="29.47265625" customWidth="true"/>
+    <col min="34" max="34" width="30.20703125" customWidth="true"/>
+    <col min="35" max="35" width="23.99609375" customWidth="true"/>
+    <col min="36" max="36" width="23.83984375" customWidth="true"/>
+    <col min="37" max="37" width="24.578125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -155,43 +261,100 @@
         <v>5</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I1" s="0" t="s">
         <v>9</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="K1" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="0" t="s">
-        <v>12</v>
-      </c>
       <c r="M1" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>18</v>
+        <v>28</v>
+      </c>
+      <c r="S1" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="T1" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="U1" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="V1" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="W1" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="X1" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y1" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z1" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA1" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB1" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC1" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD1" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE1" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF1" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG1" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH1" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI1" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ1" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="AK1" s="0" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="2">
@@ -217,28 +380,28 @@
         <v>-0.098848684736707604</v>
       </c>
       <c r="H2" s="0">
-        <v>-20.600359082079432</v>
+        <v>-1.974206672688017</v>
       </c>
       <c r="I2" s="0">
         <v>-20.600359082079432</v>
       </c>
       <c r="J2" s="0">
+        <v>-20.600359082079432</v>
+      </c>
+      <c r="K2" s="0">
+        <v>-15.43218935279398</v>
+      </c>
+      <c r="L2" s="0">
         <v>0.092488820828829602</v>
       </c>
-      <c r="K2" s="0">
+      <c r="M2" s="0">
         <v>0.092488820828829602</v>
       </c>
-      <c r="L2" s="0">
-        <v>0</v>
-      </c>
-      <c r="M2" s="0">
-        <v>0</v>
-      </c>
       <c r="N2" s="0">
-        <v>0</v>
+        <v>-0.082108118137930633</v>
       </c>
       <c r="O2" s="0">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="P2" s="0">
         <v>0</v>
@@ -248,6 +411,63 @@
       </c>
       <c r="R2" s="0">
         <v>0</v>
+      </c>
+      <c r="S2" s="0">
+        <v>0</v>
+      </c>
+      <c r="T2" s="0">
+        <v>0</v>
+      </c>
+      <c r="U2" s="0">
+        <v>0</v>
+      </c>
+      <c r="V2" s="0">
+        <v>0</v>
+      </c>
+      <c r="W2" s="0">
+        <v>42</v>
+      </c>
+      <c r="X2" s="0">
+        <v>100</v>
+      </c>
+      <c r="Y2" s="0">
+        <v>100</v>
+      </c>
+      <c r="Z2" s="0">
+        <v>100</v>
+      </c>
+      <c r="AA2" s="0">
+        <v>75.498007968127496</v>
+      </c>
+      <c r="AB2" s="0">
+        <v>7.3999999999999995</v>
+      </c>
+      <c r="AC2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="0">
+        <v>-1.8753579879513094</v>
+      </c>
+      <c r="AF2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="0">
+        <v>5.168169729285454</v>
+      </c>
+      <c r="AI2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AK2" s="0">
+        <v>-0.17459693896676023</v>
       </c>
     </row>
     <row r="3">
@@ -273,28 +493,28 @@
         <v>30.833199910339747</v>
       </c>
       <c r="H3" s="0">
-        <v>-6.356251525301893</v>
+        <v>22.81285696198443</v>
       </c>
       <c r="I3" s="0">
         <v>-6.356251525301893</v>
       </c>
       <c r="J3" s="0">
+        <v>-6.356251525301893</v>
+      </c>
+      <c r="K3" s="0">
+        <v>-4.943631055858666</v>
+      </c>
+      <c r="L3" s="0">
         <v>2.1462149309842649</v>
       </c>
-      <c r="K3" s="0">
+      <c r="M3" s="0">
         <v>2.1462149309842649</v>
       </c>
-      <c r="L3" s="0">
-        <v>0</v>
-      </c>
-      <c r="M3" s="0">
-        <v>0</v>
-      </c>
       <c r="N3" s="0">
-        <v>0</v>
+        <v>2.1195382198829535</v>
       </c>
       <c r="O3" s="0">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="P3" s="0">
         <v>0</v>
@@ -304,6 +524,63 @@
       </c>
       <c r="R3" s="0">
         <v>0</v>
+      </c>
+      <c r="S3" s="0">
+        <v>0</v>
+      </c>
+      <c r="T3" s="0">
+        <v>0</v>
+      </c>
+      <c r="U3" s="0">
+        <v>0</v>
+      </c>
+      <c r="V3" s="0">
+        <v>0</v>
+      </c>
+      <c r="W3" s="0">
+        <v>24</v>
+      </c>
+      <c r="X3" s="0">
+        <v>100</v>
+      </c>
+      <c r="Y3" s="0">
+        <v>100</v>
+      </c>
+      <c r="Z3" s="0">
+        <v>100</v>
+      </c>
+      <c r="AA3" s="0">
+        <v>79.623015873015888</v>
+      </c>
+      <c r="AB3" s="0">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AC3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="0">
+        <v>-8.020342948355319</v>
+      </c>
+      <c r="AF3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="0">
+        <v>1.4126204694432265</v>
+      </c>
+      <c r="AI3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="0">
+        <v>-0.026676711101311312</v>
       </c>
     </row>
     <row r="4">
@@ -323,43 +600,100 @@
         <v>44196</v>
       </c>
       <c r="F4" s="0">
+        <v>33.461827455645007</v>
+      </c>
+      <c r="G4" s="0">
         <v>54.809364982503439</v>
       </c>
-      <c r="G4" s="0">
-        <v>33.461827455645007</v>
-      </c>
       <c r="H4" s="0">
-        <v>-12.6912408004352</v>
+        <v>41.354662663869313</v>
       </c>
       <c r="I4" s="0">
         <v>-31.269528703541372</v>
       </c>
       <c r="J4" s="0">
+        <v>-12.6912408004352</v>
+      </c>
+      <c r="K4" s="0">
+        <v>-8.8420145949877131</v>
+      </c>
+      <c r="L4" s="0">
+        <v>1.0040977502243584</v>
+      </c>
+      <c r="M4" s="0">
         <v>2.0229901498553757</v>
       </c>
-      <c r="K4" s="0">
-        <v>1.0040977502243584</v>
-      </c>
-      <c r="L4" s="0">
+      <c r="N4" s="0">
+        <v>1.9569382150223407</v>
+      </c>
+      <c r="O4" s="0">
+        <v>1</v>
+      </c>
+      <c r="P4" s="0">
         <v>2</v>
       </c>
-      <c r="M4" s="0">
+      <c r="Q4" s="0">
         <v>2</v>
       </c>
-      <c r="N4" s="0">
+      <c r="R4" s="0">
+        <v>0</v>
+      </c>
+      <c r="S4" s="0">
+        <v>2</v>
+      </c>
+      <c r="T4" s="0">
+        <v>2</v>
+      </c>
+      <c r="U4" s="0">
+        <v>0</v>
+      </c>
+      <c r="V4" s="0">
         <v>4</v>
       </c>
-      <c r="O4" s="0">
+      <c r="W4" s="0">
+        <v>38</v>
+      </c>
+      <c r="X4" s="0">
+        <v>100</v>
+      </c>
+      <c r="Y4" s="0">
         <v>88.537549407114625</v>
       </c>
-      <c r="P4" s="0">
-        <v>21.347537526858432</v>
-      </c>
-      <c r="Q4" s="0">
+      <c r="Z4" s="0">
+        <v>88.537549407114625</v>
+      </c>
+      <c r="AA4" s="0">
+        <v>71.166007905138358</v>
+      </c>
+      <c r="AB4" s="0">
+        <v>9.0999999999999996</v>
+      </c>
+      <c r="AC4" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="0">
+        <v>21.347537526858428</v>
+      </c>
+      <c r="AE4" s="0">
+        <v>7.8928352082243025</v>
+      </c>
+      <c r="AF4" s="0">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="0">
         <v>18.578287903106173</v>
       </c>
-      <c r="R4" s="0">
+      <c r="AH4" s="0">
+        <v>22.427514108553659</v>
+      </c>
+      <c r="AI4" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="0">
         <v>1.0188923996310173</v>
+      </c>
+      <c r="AK4" s="0">
+        <v>0.95284046479798223</v>
       </c>
     </row>
     <row r="5">
@@ -385,28 +719,28 @@
         <v>32.015213727564998</v>
       </c>
       <c r="H5" s="0">
-        <v>-8.6956597355075438</v>
+        <v>21.682877916262775</v>
       </c>
       <c r="I5" s="0">
         <v>-8.6956597355075438</v>
       </c>
       <c r="J5" s="0">
+        <v>-8.6956597355075438</v>
+      </c>
+      <c r="K5" s="0">
+        <v>-5.9913175546823521</v>
+      </c>
+      <c r="L5" s="0">
         <v>1.7876078295184563</v>
       </c>
-      <c r="K5" s="0">
+      <c r="M5" s="0">
         <v>1.7876078295184563</v>
       </c>
-      <c r="L5" s="0">
-        <v>0</v>
-      </c>
-      <c r="M5" s="0">
-        <v>0</v>
-      </c>
       <c r="N5" s="0">
-        <v>0</v>
+        <v>1.6923037895473474</v>
       </c>
       <c r="O5" s="0">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="P5" s="0">
         <v>0</v>
@@ -416,6 +750,63 @@
       </c>
       <c r="R5" s="0">
         <v>0</v>
+      </c>
+      <c r="S5" s="0">
+        <v>0</v>
+      </c>
+      <c r="T5" s="0">
+        <v>0</v>
+      </c>
+      <c r="U5" s="0">
+        <v>0</v>
+      </c>
+      <c r="V5" s="0">
+        <v>0</v>
+      </c>
+      <c r="W5" s="0">
+        <v>36</v>
+      </c>
+      <c r="X5" s="0">
+        <v>100</v>
+      </c>
+      <c r="Y5" s="0">
+        <v>100</v>
+      </c>
+      <c r="Z5" s="0">
+        <v>100</v>
+      </c>
+      <c r="AA5" s="0">
+        <v>78.492063492063508</v>
+      </c>
+      <c r="AB5" s="0">
+        <v>6.5999999999999988</v>
+      </c>
+      <c r="AC5" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="0">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="0">
+        <v>-10.332335811302219</v>
+      </c>
+      <c r="AF5" s="0">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="0">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="0">
+        <v>2.7043421808251922</v>
+      </c>
+      <c r="AI5" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="0">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="0">
+        <v>-0.095304039971108923</v>
       </c>
     </row>
     <row r="6">
@@ -435,43 +826,100 @@
         <v>44926</v>
       </c>
       <c r="F6" s="0">
+        <v>-29.612779996527159</v>
+      </c>
+      <c r="G6" s="0">
         <v>-17.994638405375142</v>
       </c>
-      <c r="G6" s="0">
-        <v>-29.612779996527159</v>
-      </c>
       <c r="H6" s="0">
-        <v>-24.25527788232602</v>
+        <v>-15.712129216233928</v>
       </c>
       <c r="I6" s="0">
         <v>-32.261519608180947</v>
       </c>
       <c r="J6" s="0">
+        <v>-24.25527788232602</v>
+      </c>
+      <c r="K6" s="0">
+        <v>-18.376117357469379</v>
+      </c>
+      <c r="L6" s="0">
+        <v>-0.99513231032002081</v>
+      </c>
+      <c r="M6" s="0">
         <v>-0.73780157598627927</v>
       </c>
-      <c r="K6" s="0">
-        <v>-0.99513231032002081</v>
-      </c>
-      <c r="L6" s="0">
+      <c r="N6" s="0">
+        <v>-0.9262942055154606</v>
+      </c>
+      <c r="O6" s="0">
+        <v>1</v>
+      </c>
+      <c r="P6" s="0">
         <v>4</v>
       </c>
-      <c r="M6" s="0">
+      <c r="Q6" s="0">
         <v>4</v>
       </c>
-      <c r="N6" s="0">
+      <c r="R6" s="0">
+        <v>0</v>
+      </c>
+      <c r="S6" s="0">
+        <v>4</v>
+      </c>
+      <c r="T6" s="0">
+        <v>4</v>
+      </c>
+      <c r="U6" s="0">
+        <v>0</v>
+      </c>
+      <c r="V6" s="0">
         <v>8</v>
       </c>
-      <c r="O6" s="0">
+      <c r="W6" s="0">
+        <v>44</v>
+      </c>
+      <c r="X6" s="0">
+        <v>100</v>
+      </c>
+      <c r="Y6" s="0">
         <v>66.135458167330668</v>
       </c>
-      <c r="P6" s="0">
-        <v>11.618141591152018</v>
-      </c>
-      <c r="Q6" s="0">
-        <v>8.0062417258549274</v>
-      </c>
-      <c r="R6" s="0">
+      <c r="Z6" s="0">
+        <v>66.135458167330668</v>
+      </c>
+      <c r="AA6" s="0">
+        <v>49.601593625498012</v>
+      </c>
+      <c r="AB6" s="0">
+        <v>11.899999999999999</v>
+      </c>
+      <c r="AC6" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="0">
+        <v>11.618141591152021</v>
+      </c>
+      <c r="AE6" s="0">
+        <v>13.900650780293233</v>
+      </c>
+      <c r="AF6" s="0">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="0">
+        <v>8.0062417258549239</v>
+      </c>
+      <c r="AH6" s="0">
+        <v>13.885402250711564</v>
+      </c>
+      <c r="AI6" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="0">
         <v>0.25733073433374154</v>
+      </c>
+      <c r="AK6" s="0">
+        <v>0.068838104804560207</v>
       </c>
     </row>
     <row r="7">
@@ -497,28 +945,28 @@
         <v>28.399447404775955</v>
       </c>
       <c r="H7" s="0">
-        <v>-9.3337573541103609</v>
+        <v>20.969367677157514</v>
       </c>
       <c r="I7" s="0">
         <v>-9.3337573541103609</v>
       </c>
       <c r="J7" s="0">
+        <v>-9.3337573541103609</v>
+      </c>
+      <c r="K7" s="0">
+        <v>-6.9665251252385545</v>
+      </c>
+      <c r="L7" s="0">
         <v>1.957335080270544</v>
       </c>
-      <c r="K7" s="0">
+      <c r="M7" s="0">
         <v>1.957335080270544</v>
       </c>
-      <c r="L7" s="0">
-        <v>0</v>
-      </c>
-      <c r="M7" s="0">
-        <v>0</v>
-      </c>
       <c r="N7" s="0">
-        <v>0</v>
+        <v>1.9105805296142842</v>
       </c>
       <c r="O7" s="0">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="P7" s="0">
         <v>0</v>
@@ -528,6 +976,63 @@
       </c>
       <c r="R7" s="0">
         <v>0</v>
+      </c>
+      <c r="S7" s="0">
+        <v>0</v>
+      </c>
+      <c r="T7" s="0">
+        <v>0</v>
+      </c>
+      <c r="U7" s="0">
+        <v>0</v>
+      </c>
+      <c r="V7" s="0">
+        <v>0</v>
+      </c>
+      <c r="W7" s="0">
+        <v>33</v>
+      </c>
+      <c r="X7" s="0">
+        <v>100</v>
+      </c>
+      <c r="Y7" s="0">
+        <v>100</v>
+      </c>
+      <c r="Z7" s="0">
+        <v>100</v>
+      </c>
+      <c r="AA7" s="0">
+        <v>78.040000000000006</v>
+      </c>
+      <c r="AB7" s="0">
+        <v>5.8999999999999986</v>
+      </c>
+      <c r="AC7" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="0">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="0">
+        <v>-7.4300797276184438</v>
+      </c>
+      <c r="AF7" s="0">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="0">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="0">
+        <v>2.3672322288718073</v>
+      </c>
+      <c r="AI7" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="0">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="0">
+        <v>-0.046754550656259886</v>
       </c>
     </row>
     <row r="8">
@@ -553,28 +1058,28 @@
         <v>35.106055948355184</v>
       </c>
       <c r="H8" s="0">
-        <v>-12.746730083234258</v>
+        <v>23.0277985399578</v>
       </c>
       <c r="I8" s="0">
         <v>-12.746730083234258</v>
       </c>
       <c r="J8" s="0">
+        <v>-12.746730083234258</v>
+      </c>
+      <c r="K8" s="0">
+        <v>-9.6458021976037358</v>
+      </c>
+      <c r="L8" s="0">
         <v>1.7924158170424755</v>
       </c>
-      <c r="K8" s="0">
+      <c r="M8" s="0">
         <v>1.7924158170424755</v>
       </c>
-      <c r="L8" s="0">
-        <v>0</v>
-      </c>
-      <c r="M8" s="0">
-        <v>0</v>
-      </c>
       <c r="N8" s="0">
-        <v>0</v>
+        <v>1.6338795575801175</v>
       </c>
       <c r="O8" s="0">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="P8" s="0">
         <v>0</v>
@@ -584,6 +1089,63 @@
       </c>
       <c r="R8" s="0">
         <v>0</v>
+      </c>
+      <c r="S8" s="0">
+        <v>0</v>
+      </c>
+      <c r="T8" s="0">
+        <v>0</v>
+      </c>
+      <c r="U8" s="0">
+        <v>0</v>
+      </c>
+      <c r="V8" s="0">
+        <v>0</v>
+      </c>
+      <c r="W8" s="0">
+        <v>48</v>
+      </c>
+      <c r="X8" s="0">
+        <v>100</v>
+      </c>
+      <c r="Y8" s="0">
+        <v>100</v>
+      </c>
+      <c r="Z8" s="0">
+        <v>100</v>
+      </c>
+      <c r="AA8" s="0">
+        <v>78.809523809523824</v>
+      </c>
+      <c r="AB8" s="0">
+        <v>8.3999999999999986</v>
+      </c>
+      <c r="AC8" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="0">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="0">
+        <v>-12.078257408397386</v>
+      </c>
+      <c r="AF8" s="0">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="0">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="0">
+        <v>3.1009278856305222</v>
+      </c>
+      <c r="AI8" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="0">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="0">
+        <v>-0.15853625946235805</v>
       </c>
     </row>
     <row r="9">
@@ -603,43 +1165,100 @@
         <v>46022</v>
       </c>
       <c r="F9" s="0">
+        <v>21.387940841865927</v>
+      </c>
+      <c r="G9" s="0">
         <v>19.898450918230147</v>
       </c>
-      <c r="G9" s="0">
-        <v>21.387940841865927</v>
-      </c>
       <c r="H9" s="0">
-        <v>-23.207478665404135</v>
+        <v>10.738016919695138</v>
       </c>
       <c r="I9" s="0">
         <v>-22.253490637514915</v>
       </c>
       <c r="J9" s="0">
+        <v>-23.207478665404135</v>
+      </c>
+      <c r="K9" s="0">
+        <v>-17.945501638200057</v>
+      </c>
+      <c r="L9" s="0">
+        <v>0.95343034850768338</v>
+      </c>
+      <c r="M9" s="0">
         <v>0.92463872031323802</v>
       </c>
-      <c r="K9" s="0">
-        <v>0.95343034850768338</v>
-      </c>
-      <c r="L9" s="0">
-        <v>1</v>
-      </c>
-      <c r="M9" s="0">
-        <v>1</v>
-      </c>
       <c r="N9" s="0">
+        <v>0.73851330568740958</v>
+      </c>
+      <c r="O9" s="0">
+        <v>1</v>
+      </c>
+      <c r="P9" s="0">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="0">
+        <v>1</v>
+      </c>
+      <c r="R9" s="0">
+        <v>0</v>
+      </c>
+      <c r="S9" s="0">
+        <v>1</v>
+      </c>
+      <c r="T9" s="0">
+        <v>1</v>
+      </c>
+      <c r="U9" s="0">
+        <v>0</v>
+      </c>
+      <c r="V9" s="0">
         <v>2</v>
       </c>
-      <c r="O9" s="0">
+      <c r="W9" s="0">
+        <v>44</v>
+      </c>
+      <c r="X9" s="0">
+        <v>100</v>
+      </c>
+      <c r="Y9" s="0">
         <v>95.199999999999989</v>
       </c>
-      <c r="P9" s="0">
-        <v>-1.4894899236357801</v>
-      </c>
-      <c r="Q9" s="0">
-        <v>-0.95398802788922055</v>
-      </c>
-      <c r="R9" s="0">
+      <c r="Z9" s="0">
+        <v>95.199999999999989</v>
+      </c>
+      <c r="AA9" s="0">
+        <v>74.000000000000028</v>
+      </c>
+      <c r="AB9" s="0">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="AC9" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="0">
+        <v>-1.4894899236357784</v>
+      </c>
+      <c r="AE9" s="0">
+        <v>-10.649923922170789</v>
+      </c>
+      <c r="AF9" s="0">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="0">
+        <v>-0.95398802788921877</v>
+      </c>
+      <c r="AH9" s="0">
+        <v>4.3079889993148601</v>
+      </c>
+      <c r="AI9" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="0">
         <v>-0.028791628194445362</v>
+      </c>
+      <c r="AK9" s="0">
+        <v>-0.2149170428202738</v>
       </c>
     </row>
     <row r="10">
@@ -665,28 +1284,28 @@
         <v>13.870665417057083</v>
       </c>
       <c r="H10" s="0">
-        <v>-13.530655391120527</v>
+        <v>11.662601198845589</v>
       </c>
       <c r="I10" s="0">
         <v>-13.530655391120527</v>
       </c>
       <c r="J10" s="0">
+        <v>-13.530655391120527</v>
+      </c>
+      <c r="K10" s="0">
+        <v>-9.6984812445111359</v>
+      </c>
+      <c r="L10" s="0">
         <v>1.8117160195603883</v>
       </c>
-      <c r="K10" s="0">
+      <c r="M10" s="0">
         <v>1.8117160195603883</v>
       </c>
-      <c r="L10" s="0">
-        <v>0</v>
-      </c>
-      <c r="M10" s="0">
-        <v>0</v>
-      </c>
       <c r="N10" s="0">
-        <v>0</v>
+        <v>2.0491356563177874</v>
       </c>
       <c r="O10" s="0">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="P10" s="0">
         <v>0</v>
@@ -696,6 +1315,63 @@
       </c>
       <c r="R10" s="0">
         <v>0</v>
+      </c>
+      <c r="S10" s="0">
+        <v>0</v>
+      </c>
+      <c r="T10" s="0">
+        <v>0</v>
+      </c>
+      <c r="U10" s="0">
+        <v>0</v>
+      </c>
+      <c r="V10" s="0">
+        <v>0</v>
+      </c>
+      <c r="W10" s="0">
+        <v>14</v>
+      </c>
+      <c r="X10" s="0">
+        <v>100</v>
+      </c>
+      <c r="Y10" s="0">
+        <v>100</v>
+      </c>
+      <c r="Z10" s="0">
+        <v>100</v>
+      </c>
+      <c r="AA10" s="0">
+        <v>76.323529411764724</v>
+      </c>
+      <c r="AB10" s="0">
+        <v>2.5999999999999996</v>
+      </c>
+      <c r="AC10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="0">
+        <v>-2.2080642182114918</v>
+      </c>
+      <c r="AF10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="0">
+        <v>3.8321741466093906</v>
+      </c>
+      <c r="AI10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="0">
+        <v>0.23741963675739908</v>
       </c>
     </row>
   </sheetData>

--- a/results/walkforward/walk_forward_SPYG.xlsx
+++ b/results/walkforward/walk_forward_SPYG.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="181" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="273" uniqueCount="48">
   <si>
     <t>Ticker</t>
   </si>
@@ -218,7 +218,7 @@
     <col min="11" max="11" width="22.89453125" customWidth="true"/>
     <col min="12" max="12" width="13.578125" customWidth="true"/>
     <col min="13" max="13" width="13.578125" customWidth="true"/>
-    <col min="14" max="14" width="14.15625" customWidth="true"/>
+    <col min="14" max="14" width="13.7890625" customWidth="true"/>
     <col min="15" max="15" width="15.41796875" customWidth="true"/>
     <col min="16" max="16" width="15.26171875" customWidth="true"/>
     <col min="17" max="17" width="16" customWidth="true"/>
@@ -380,7 +380,7 @@
         <v>-0.098848684736707604</v>
       </c>
       <c r="H2" s="0">
-        <v>-1.974206672688017</v>
+        <v>-4.8417640148233243</v>
       </c>
       <c r="I2" s="0">
         <v>-20.600359082079432</v>
@@ -389,7 +389,7 @@
         <v>-20.600359082079432</v>
       </c>
       <c r="K2" s="0">
-        <v>-15.43218935279398</v>
+        <v>-20.759534061887265</v>
       </c>
       <c r="L2" s="0">
         <v>0.092488820828829602</v>
@@ -398,7 +398,7 @@
         <v>0.092488820828829602</v>
       </c>
       <c r="N2" s="0">
-        <v>-0.082108118137930633</v>
+        <v>-0.17156483496475169</v>
       </c>
       <c r="O2" s="0">
         <v>1</v>
@@ -425,7 +425,7 @@
         <v>0</v>
       </c>
       <c r="W2" s="0">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="X2" s="0">
         <v>100</v>
@@ -437,10 +437,10 @@
         <v>100</v>
       </c>
       <c r="AA2" s="0">
-        <v>75.498007968127496</v>
+        <v>97.908366533864537</v>
       </c>
       <c r="AB2" s="0">
-        <v>7.3999999999999995</v>
+        <v>4</v>
       </c>
       <c r="AC2" s="0">
         <v>0</v>
@@ -449,7 +449,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="0">
-        <v>-1.8753579879513094</v>
+        <v>-4.7429153300866167</v>
       </c>
       <c r="AF2" s="0">
         <v>0</v>
@@ -458,7 +458,7 @@
         <v>0</v>
       </c>
       <c r="AH2" s="0">
-        <v>5.168169729285454</v>
+        <v>-0.15917497980783013</v>
       </c>
       <c r="AI2" s="0">
         <v>0</v>
@@ -467,7 +467,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="0">
-        <v>-0.17459693896676023</v>
+        <v>-0.26405365579358131</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>30.833199910339747</v>
       </c>
       <c r="H3" s="0">
-        <v>22.81285696198443</v>
+        <v>30.833199910339747</v>
       </c>
       <c r="I3" s="0">
         <v>-6.356251525301893</v>
@@ -502,7 +502,7 @@
         <v>-6.356251525301893</v>
       </c>
       <c r="K3" s="0">
-        <v>-4.943631055858666</v>
+        <v>-6.356251525301893</v>
       </c>
       <c r="L3" s="0">
         <v>2.1462149309842649</v>
@@ -511,7 +511,7 @@
         <v>2.1462149309842649</v>
       </c>
       <c r="N3" s="0">
-        <v>2.1195382198829535</v>
+        <v>2.1462149309842649</v>
       </c>
       <c r="O3" s="0">
         <v>1</v>
@@ -538,7 +538,7 @@
         <v>0</v>
       </c>
       <c r="W3" s="0">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X3" s="0">
         <v>100</v>
@@ -550,10 +550,10 @@
         <v>100</v>
       </c>
       <c r="AA3" s="0">
-        <v>79.623015873015888</v>
+        <v>100</v>
       </c>
       <c r="AB3" s="0">
-        <v>4.5999999999999996</v>
+        <v>0</v>
       </c>
       <c r="AC3" s="0">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="AE3" s="0">
-        <v>-8.020342948355319</v>
+        <v>0</v>
       </c>
       <c r="AF3" s="0">
         <v>0</v>
@@ -571,7 +571,7 @@
         <v>0</v>
       </c>
       <c r="AH3" s="0">
-        <v>1.4126204694432265</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="0">
         <v>0</v>
@@ -580,7 +580,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="0">
-        <v>-0.026676711101311312</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -606,7 +606,7 @@
         <v>54.809364982503439</v>
       </c>
       <c r="H4" s="0">
-        <v>41.354662663869313</v>
+        <v>53.62589937415698</v>
       </c>
       <c r="I4" s="0">
         <v>-31.269528703541372</v>
@@ -615,7 +615,7 @@
         <v>-12.6912408004352</v>
       </c>
       <c r="K4" s="0">
-        <v>-8.8420145949877131</v>
+        <v>-12.6912408004352</v>
       </c>
       <c r="L4" s="0">
         <v>1.0040977502243584</v>
@@ -624,7 +624,7 @@
         <v>2.0229901498553757</v>
       </c>
       <c r="N4" s="0">
-        <v>1.9569382150223407</v>
+        <v>2.0719847041114186</v>
       </c>
       <c r="O4" s="0">
         <v>1</v>
@@ -651,7 +651,7 @@
         <v>4</v>
       </c>
       <c r="W4" s="0">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="X4" s="0">
         <v>100</v>
@@ -663,10 +663,10 @@
         <v>88.537549407114625</v>
       </c>
       <c r="AA4" s="0">
-        <v>71.166007905138358</v>
+        <v>87.154150197628454</v>
       </c>
       <c r="AB4" s="0">
-        <v>9.0999999999999996</v>
+        <v>4.5</v>
       </c>
       <c r="AC4" s="0">
         <v>0</v>
@@ -675,7 +675,7 @@
         <v>21.347537526858428</v>
       </c>
       <c r="AE4" s="0">
-        <v>7.8928352082243025</v>
+        <v>20.164071918511972</v>
       </c>
       <c r="AF4" s="0">
         <v>0</v>
@@ -684,7 +684,7 @@
         <v>18.578287903106173</v>
       </c>
       <c r="AH4" s="0">
-        <v>22.427514108553659</v>
+        <v>18.578287903106173</v>
       </c>
       <c r="AI4" s="0">
         <v>0</v>
@@ -693,7 +693,7 @@
         <v>1.0188923996310173</v>
       </c>
       <c r="AK4" s="0">
-        <v>0.95284046479798223</v>
+        <v>1.0678869538870601</v>
       </c>
     </row>
     <row r="5">
@@ -719,7 +719,7 @@
         <v>32.015213727564998</v>
       </c>
       <c r="H5" s="0">
-        <v>21.682877916262775</v>
+        <v>30.974871267520676</v>
       </c>
       <c r="I5" s="0">
         <v>-8.6956597355075438</v>
@@ -728,7 +728,7 @@
         <v>-8.6956597355075438</v>
       </c>
       <c r="K5" s="0">
-        <v>-5.9913175546823521</v>
+        <v>-8.7189750481749364</v>
       </c>
       <c r="L5" s="0">
         <v>1.7876078295184563</v>
@@ -737,7 +737,7 @@
         <v>1.7876078295184563</v>
       </c>
       <c r="N5" s="0">
-        <v>1.6923037895473474</v>
+        <v>1.7507055129466425</v>
       </c>
       <c r="O5" s="0">
         <v>1</v>
@@ -764,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="W5" s="0">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="X5" s="0">
         <v>100</v>
@@ -776,10 +776,10 @@
         <v>100</v>
       </c>
       <c r="AA5" s="0">
-        <v>78.492063492063508</v>
+        <v>99.900793650793645</v>
       </c>
       <c r="AB5" s="0">
-        <v>6.5999999999999988</v>
+        <v>0.5</v>
       </c>
       <c r="AC5" s="0">
         <v>0</v>
@@ -788,7 +788,7 @@
         <v>0</v>
       </c>
       <c r="AE5" s="0">
-        <v>-10.332335811302219</v>
+        <v>-1.040342460044319</v>
       </c>
       <c r="AF5" s="0">
         <v>0</v>
@@ -797,7 +797,7 @@
         <v>0</v>
       </c>
       <c r="AH5" s="0">
-        <v>2.7043421808251922</v>
+        <v>-0.023315312667393506</v>
       </c>
       <c r="AI5" s="0">
         <v>0</v>
@@ -806,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="0">
-        <v>-0.095304039971108923</v>
+        <v>-0.036902316571813865</v>
       </c>
     </row>
     <row r="6">
@@ -832,7 +832,7 @@
         <v>-17.994638405375142</v>
       </c>
       <c r="H6" s="0">
-        <v>-15.712129216233928</v>
+        <v>-18.285382953505891</v>
       </c>
       <c r="I6" s="0">
         <v>-32.261519608180947</v>
@@ -841,7 +841,7 @@
         <v>-24.25527788232602</v>
       </c>
       <c r="K6" s="0">
-        <v>-18.376117357469379</v>
+        <v>-22.541241248138189</v>
       </c>
       <c r="L6" s="0">
         <v>-0.99513231032002081</v>
@@ -850,7 +850,7 @@
         <v>-0.73780157598627927</v>
       </c>
       <c r="N6" s="0">
-        <v>-0.9262942055154606</v>
+        <v>-0.79549206198540079</v>
       </c>
       <c r="O6" s="0">
         <v>1</v>
@@ -877,7 +877,7 @@
         <v>8</v>
       </c>
       <c r="W6" s="0">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="X6" s="0">
         <v>100</v>
@@ -889,10 +889,10 @@
         <v>66.135458167330668</v>
       </c>
       <c r="AA6" s="0">
-        <v>49.601593625498012</v>
+        <v>63.34661354581673</v>
       </c>
       <c r="AB6" s="0">
-        <v>11.899999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="AC6" s="0">
         <v>0</v>
@@ -901,7 +901,7 @@
         <v>11.618141591152021</v>
       </c>
       <c r="AE6" s="0">
-        <v>13.900650780293233</v>
+        <v>11.32739704302127</v>
       </c>
       <c r="AF6" s="0">
         <v>0</v>
@@ -910,7 +910,7 @@
         <v>8.0062417258549239</v>
       </c>
       <c r="AH6" s="0">
-        <v>13.885402250711564</v>
+        <v>9.7202783600427551</v>
       </c>
       <c r="AI6" s="0">
         <v>0</v>
@@ -919,7 +919,7 @@
         <v>0.25733073433374154</v>
       </c>
       <c r="AK6" s="0">
-        <v>0.068838104804560207</v>
+        <v>0.19964024833462002</v>
       </c>
     </row>
     <row r="7">
@@ -945,7 +945,7 @@
         <v>28.399447404775955</v>
       </c>
       <c r="H7" s="0">
-        <v>20.969367677157514</v>
+        <v>27.689189804330326</v>
       </c>
       <c r="I7" s="0">
         <v>-9.3337573541103609</v>
@@ -954,7 +954,7 @@
         <v>-9.3337573541103609</v>
       </c>
       <c r="K7" s="0">
-        <v>-6.9665251252385545</v>
+        <v>-9.5161786582947485</v>
       </c>
       <c r="L7" s="0">
         <v>1.957335080270544</v>
@@ -963,7 +963,7 @@
         <v>1.957335080270544</v>
       </c>
       <c r="N7" s="0">
-        <v>1.9105805296142842</v>
+        <v>1.9194434842835171</v>
       </c>
       <c r="O7" s="0">
         <v>1</v>
@@ -990,7 +990,7 @@
         <v>0</v>
       </c>
       <c r="W7" s="0">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="X7" s="0">
         <v>100</v>
@@ -1002,10 +1002,10 @@
         <v>100</v>
       </c>
       <c r="AA7" s="0">
-        <v>78.040000000000006</v>
+        <v>99.799999999999997</v>
       </c>
       <c r="AB7" s="0">
-        <v>5.8999999999999986</v>
+        <v>1</v>
       </c>
       <c r="AC7" s="0">
         <v>0</v>
@@ -1014,7 +1014,7 @@
         <v>0</v>
       </c>
       <c r="AE7" s="0">
-        <v>-7.4300797276184438</v>
+        <v>-0.71025760044562958</v>
       </c>
       <c r="AF7" s="0">
         <v>0</v>
@@ -1023,7 +1023,7 @@
         <v>0</v>
       </c>
       <c r="AH7" s="0">
-        <v>2.3672322288718073</v>
+        <v>-0.18242130418438807</v>
       </c>
       <c r="AI7" s="0">
         <v>0</v>
@@ -1032,7 +1032,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="0">
-        <v>-0.046754550656259886</v>
+        <v>-0.03789159598702696</v>
       </c>
     </row>
     <row r="8">
@@ -1058,7 +1058,7 @@
         <v>35.106055948355184</v>
       </c>
       <c r="H8" s="0">
-        <v>23.0277985399578</v>
+        <v>33.555952506321304</v>
       </c>
       <c r="I8" s="0">
         <v>-12.746730083234258</v>
@@ -1067,7 +1067,7 @@
         <v>-12.746730083234258</v>
       </c>
       <c r="K8" s="0">
-        <v>-9.6458021976037358</v>
+        <v>-13.082199302736541</v>
       </c>
       <c r="L8" s="0">
         <v>1.7924158170424755</v>
@@ -1076,7 +1076,7 @@
         <v>1.7924158170424755</v>
       </c>
       <c r="N8" s="0">
-        <v>1.6338795575801175</v>
+        <v>1.7422277666827779</v>
       </c>
       <c r="O8" s="0">
         <v>1</v>
@@ -1103,7 +1103,7 @@
         <v>0</v>
       </c>
       <c r="W8" s="0">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="X8" s="0">
         <v>100</v>
@@ -1115,10 +1115,10 @@
         <v>100</v>
       </c>
       <c r="AA8" s="0">
-        <v>78.809523809523824</v>
+        <v>99.603174603174608</v>
       </c>
       <c r="AB8" s="0">
-        <v>8.3999999999999986</v>
+        <v>1</v>
       </c>
       <c r="AC8" s="0">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="AE8" s="0">
-        <v>-12.078257408397386</v>
+        <v>-1.5501034420338788</v>
       </c>
       <c r="AF8" s="0">
         <v>0</v>
@@ -1136,7 +1136,7 @@
         <v>0</v>
       </c>
       <c r="AH8" s="0">
-        <v>3.1009278856305222</v>
+        <v>-0.33546921950228237</v>
       </c>
       <c r="AI8" s="0">
         <v>0</v>
@@ -1145,7 +1145,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="0">
-        <v>-0.15853625946235805</v>
+        <v>-0.050188050359697645</v>
       </c>
     </row>
     <row r="9">
@@ -1171,7 +1171,7 @@
         <v>19.898450918230147</v>
       </c>
       <c r="H9" s="0">
-        <v>10.738016919695138</v>
+        <v>20.875150582990077</v>
       </c>
       <c r="I9" s="0">
         <v>-22.253490637514915</v>
@@ -1180,7 +1180,7 @@
         <v>-23.207478665404135</v>
       </c>
       <c r="K9" s="0">
-        <v>-17.945501638200057</v>
+        <v>-22.300702067618861</v>
       </c>
       <c r="L9" s="0">
         <v>0.95343034850768338</v>
@@ -1189,7 +1189,7 @@
         <v>0.92463872031323802</v>
       </c>
       <c r="N9" s="0">
-        <v>0.73851330568740958</v>
+        <v>0.977374703633624</v>
       </c>
       <c r="O9" s="0">
         <v>1</v>
@@ -1216,7 +1216,7 @@
         <v>2</v>
       </c>
       <c r="W9" s="0">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="X9" s="0">
         <v>100</v>
@@ -1228,10 +1228,10 @@
         <v>95.199999999999989</v>
       </c>
       <c r="AA9" s="0">
-        <v>74.000000000000028</v>
+        <v>94.299999999999997</v>
       </c>
       <c r="AB9" s="0">
-        <v>9.1999999999999993</v>
+        <v>3</v>
       </c>
       <c r="AC9" s="0">
         <v>0</v>
@@ -1240,7 +1240,7 @@
         <v>-1.4894899236357784</v>
       </c>
       <c r="AE9" s="0">
-        <v>-10.649923922170789</v>
+        <v>-0.51279025887585039</v>
       </c>
       <c r="AF9" s="0">
         <v>0</v>
@@ -1249,7 +1249,7 @@
         <v>-0.95398802788921877</v>
       </c>
       <c r="AH9" s="0">
-        <v>4.3079889993148601</v>
+        <v>-0.047211430103943908</v>
       </c>
       <c r="AI9" s="0">
         <v>0</v>
@@ -1258,7 +1258,7 @@
         <v>-0.028791628194445362</v>
       </c>
       <c r="AK9" s="0">
-        <v>-0.2149170428202738</v>
+        <v>0.02394435512594062</v>
       </c>
     </row>
     <row r="10">
@@ -1284,7 +1284,7 @@
         <v>13.870665417057083</v>
       </c>
       <c r="H10" s="0">
-        <v>11.662601198845589</v>
+        <v>13.870665417057083</v>
       </c>
       <c r="I10" s="0">
         <v>-13.530655391120527</v>
@@ -1293,7 +1293,7 @@
         <v>-13.530655391120527</v>
       </c>
       <c r="K10" s="0">
-        <v>-9.6984812445111359</v>
+        <v>-13.530655391120527</v>
       </c>
       <c r="L10" s="0">
         <v>1.8117160195603883</v>
@@ -1302,7 +1302,7 @@
         <v>1.8117160195603883</v>
       </c>
       <c r="N10" s="0">
-        <v>2.0491356563177874</v>
+        <v>1.8117160195603883</v>
       </c>
       <c r="O10" s="0">
         <v>1</v>
@@ -1329,7 +1329,7 @@
         <v>0</v>
       </c>
       <c r="W10" s="0">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="X10" s="0">
         <v>100</v>
@@ -1341,10 +1341,10 @@
         <v>100</v>
       </c>
       <c r="AA10" s="0">
-        <v>76.323529411764724</v>
+        <v>100</v>
       </c>
       <c r="AB10" s="0">
-        <v>2.5999999999999996</v>
+        <v>0</v>
       </c>
       <c r="AC10" s="0">
         <v>0</v>
@@ -1353,7 +1353,7 @@
         <v>0</v>
       </c>
       <c r="AE10" s="0">
-        <v>-2.2080642182114918</v>
+        <v>0</v>
       </c>
       <c r="AF10" s="0">
         <v>0</v>
@@ -1362,7 +1362,7 @@
         <v>0</v>
       </c>
       <c r="AH10" s="0">
-        <v>3.8321741466093906</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="0">
         <v>0</v>
@@ -1371,7 +1371,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="0">
-        <v>0.23741963675739908</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/results/walkforward/walk_forward_SPYG.xlsx
+++ b/results/walkforward/walk_forward_SPYG.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="273" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="457" uniqueCount="48">
   <si>
     <t>Ticker</t>
   </si>
@@ -380,7 +380,7 @@
         <v>-0.098848684736707604</v>
       </c>
       <c r="H2" s="0">
-        <v>-4.8417640148233243</v>
+        <v>-3.7280665610042174</v>
       </c>
       <c r="I2" s="0">
         <v>-20.600359082079432</v>
@@ -389,7 +389,7 @@
         <v>-20.600359082079432</v>
       </c>
       <c r="K2" s="0">
-        <v>-20.759534061887265</v>
+        <v>-20.212874320140706</v>
       </c>
       <c r="L2" s="0">
         <v>0.092488820828829602</v>
@@ -398,7 +398,7 @@
         <v>0.092488820828829602</v>
       </c>
       <c r="N2" s="0">
-        <v>-0.17156483496475169</v>
+        <v>-0.10975011964925063</v>
       </c>
       <c r="O2" s="0">
         <v>1</v>
@@ -425,7 +425,7 @@
         <v>0</v>
       </c>
       <c r="W2" s="0">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="X2" s="0">
         <v>100</v>
@@ -437,10 +437,10 @@
         <v>100</v>
       </c>
       <c r="AA2" s="0">
-        <v>97.908366533864537</v>
+        <v>97.111553784860561</v>
       </c>
       <c r="AB2" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC2" s="0">
         <v>0</v>
@@ -449,7 +449,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="0">
-        <v>-4.7429153300866167</v>
+        <v>-3.6292178762675098</v>
       </c>
       <c r="AF2" s="0">
         <v>0</v>
@@ -458,7 +458,7 @@
         <v>0</v>
       </c>
       <c r="AH2" s="0">
-        <v>-0.15917497980783013</v>
+        <v>0.38748476193872783</v>
       </c>
       <c r="AI2" s="0">
         <v>0</v>
@@ -467,7 +467,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="0">
-        <v>-0.26405365579358131</v>
+        <v>-0.20223894047808022</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>30.833199910339747</v>
       </c>
       <c r="H3" s="0">
-        <v>30.833199910339747</v>
+        <v>32.602484796848465</v>
       </c>
       <c r="I3" s="0">
         <v>-6.356251525301893</v>
@@ -502,7 +502,7 @@
         <v>-6.356251525301893</v>
       </c>
       <c r="K3" s="0">
-        <v>-6.356251525301893</v>
+        <v>-6.3562515253019143</v>
       </c>
       <c r="L3" s="0">
         <v>2.1462149309842649</v>
@@ -511,7 +511,7 @@
         <v>2.1462149309842649</v>
       </c>
       <c r="N3" s="0">
-        <v>2.1462149309842649</v>
+        <v>2.2821062064228377</v>
       </c>
       <c r="O3" s="0">
         <v>1</v>
@@ -538,7 +538,7 @@
         <v>0</v>
       </c>
       <c r="W3" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" s="0">
         <v>100</v>
@@ -550,10 +550,10 @@
         <v>100</v>
       </c>
       <c r="AA3" s="0">
-        <v>100</v>
+        <v>99.801587301587304</v>
       </c>
       <c r="AB3" s="0">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AC3" s="0">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="AE3" s="0">
-        <v>0</v>
+        <v>1.7692848865087152</v>
       </c>
       <c r="AF3" s="0">
         <v>0</v>
@@ -571,7 +571,7 @@
         <v>0</v>
       </c>
       <c r="AH3" s="0">
-        <v>0</v>
+        <v>-2.2204460492503131e-14</v>
       </c>
       <c r="AI3" s="0">
         <v>0</v>
@@ -580,7 +580,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="0">
-        <v>0</v>
+        <v>0.13589127543857282</v>
       </c>
     </row>
     <row r="4">
@@ -603,28 +603,28 @@
         <v>33.461827455645007</v>
       </c>
       <c r="G4" s="0">
-        <v>54.809364982503439</v>
+        <v>48.632508085214752</v>
       </c>
       <c r="H4" s="0">
-        <v>53.62589937415698</v>
+        <v>51.460572366482204</v>
       </c>
       <c r="I4" s="0">
         <v>-31.269528703541372</v>
       </c>
       <c r="J4" s="0">
-        <v>-12.6912408004352</v>
+        <v>-13.971557711939898</v>
       </c>
       <c r="K4" s="0">
-        <v>-12.6912408004352</v>
+        <v>-12.700893998527862</v>
       </c>
       <c r="L4" s="0">
         <v>1.0040977502243584</v>
       </c>
       <c r="M4" s="0">
-        <v>2.0229901498553757</v>
+        <v>1.8435008179765755</v>
       </c>
       <c r="N4" s="0">
-        <v>2.0719847041114186</v>
+        <v>1.9864130059745821</v>
       </c>
       <c r="O4" s="0">
         <v>1</v>
@@ -657,13 +657,13 @@
         <v>100</v>
       </c>
       <c r="Y4" s="0">
-        <v>88.537549407114625</v>
+        <v>88.932806324110672</v>
       </c>
       <c r="Z4" s="0">
-        <v>88.537549407114625</v>
+        <v>88.932806324110672</v>
       </c>
       <c r="AA4" s="0">
-        <v>87.154150197628454</v>
+        <v>87.351778656126484</v>
       </c>
       <c r="AB4" s="0">
         <v>4.5</v>
@@ -672,28 +672,28 @@
         <v>0</v>
       </c>
       <c r="AD4" s="0">
-        <v>21.347537526858428</v>
+        <v>15.170680629569745</v>
       </c>
       <c r="AE4" s="0">
-        <v>20.164071918511972</v>
+        <v>17.998744910837196</v>
       </c>
       <c r="AF4" s="0">
         <v>0</v>
       </c>
       <c r="AG4" s="0">
-        <v>18.578287903106173</v>
+        <v>17.297970991601474</v>
       </c>
       <c r="AH4" s="0">
-        <v>18.578287903106173</v>
+        <v>18.568634705013508</v>
       </c>
       <c r="AI4" s="0">
         <v>0</v>
       </c>
       <c r="AJ4" s="0">
-        <v>1.0188923996310173</v>
+        <v>0.83940306775221707</v>
       </c>
       <c r="AK4" s="0">
-        <v>1.0678869538870601</v>
+        <v>0.98231525575022371</v>
       </c>
     </row>
     <row r="5">
@@ -719,7 +719,7 @@
         <v>32.015213727564998</v>
       </c>
       <c r="H5" s="0">
-        <v>30.974871267520676</v>
+        <v>32.015213727564998</v>
       </c>
       <c r="I5" s="0">
         <v>-8.6956597355075438</v>
@@ -728,7 +728,7 @@
         <v>-8.6956597355075438</v>
       </c>
       <c r="K5" s="0">
-        <v>-8.7189750481749364</v>
+        <v>-8.6956597355075438</v>
       </c>
       <c r="L5" s="0">
         <v>1.7876078295184563</v>
@@ -737,7 +737,7 @@
         <v>1.7876078295184563</v>
       </c>
       <c r="N5" s="0">
-        <v>1.7507055129466425</v>
+        <v>1.7876078295184563</v>
       </c>
       <c r="O5" s="0">
         <v>1</v>
@@ -764,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="W5" s="0">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X5" s="0">
         <v>100</v>
@@ -776,10 +776,10 @@
         <v>100</v>
       </c>
       <c r="AA5" s="0">
-        <v>99.900793650793645</v>
+        <v>100</v>
       </c>
       <c r="AB5" s="0">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AC5" s="0">
         <v>0</v>
@@ -788,7 +788,7 @@
         <v>0</v>
       </c>
       <c r="AE5" s="0">
-        <v>-1.040342460044319</v>
+        <v>0</v>
       </c>
       <c r="AF5" s="0">
         <v>0</v>
@@ -797,7 +797,7 @@
         <v>0</v>
       </c>
       <c r="AH5" s="0">
-        <v>-0.023315312667393506</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="0">
         <v>0</v>
@@ -806,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="0">
-        <v>-0.036902316571813865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -829,97 +829,97 @@
         <v>-29.612779996527159</v>
       </c>
       <c r="G6" s="0">
-        <v>-17.994638405375142</v>
+        <v>-24.245971376067644</v>
       </c>
       <c r="H6" s="0">
-        <v>-18.285382953505891</v>
+        <v>-24.460275298666957</v>
       </c>
       <c r="I6" s="0">
         <v>-32.261519608180947</v>
       </c>
       <c r="J6" s="0">
-        <v>-24.25527788232602</v>
+        <v>-29.962933741616837</v>
       </c>
       <c r="K6" s="0">
-        <v>-22.541241248138189</v>
+        <v>-28.855913190357953</v>
       </c>
       <c r="L6" s="0">
         <v>-0.99513231032002081</v>
       </c>
       <c r="M6" s="0">
-        <v>-0.73780157598627927</v>
+        <v>-1.0285799861772555</v>
       </c>
       <c r="N6" s="0">
-        <v>-0.79549206198540079</v>
+        <v>-1.0763324862253341</v>
       </c>
       <c r="O6" s="0">
         <v>1</v>
       </c>
       <c r="P6" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q6" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R6" s="0">
         <v>0</v>
       </c>
       <c r="S6" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T6" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U6" s="0">
         <v>0</v>
       </c>
       <c r="V6" s="0">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W6" s="0">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="X6" s="0">
         <v>100</v>
       </c>
       <c r="Y6" s="0">
-        <v>66.135458167330668</v>
+        <v>72.509960159362549</v>
       </c>
       <c r="Z6" s="0">
-        <v>66.135458167330668</v>
+        <v>72.509960159362549</v>
       </c>
       <c r="AA6" s="0">
-        <v>63.34661354581673</v>
+        <v>69.721115537848604</v>
       </c>
       <c r="AB6" s="0">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="AC6" s="0">
         <v>0</v>
       </c>
       <c r="AD6" s="0">
-        <v>11.618141591152021</v>
+        <v>5.3668086204595173</v>
       </c>
       <c r="AE6" s="0">
-        <v>11.32739704302127</v>
+        <v>5.1525046978602056</v>
       </c>
       <c r="AF6" s="0">
         <v>0</v>
       </c>
       <c r="AG6" s="0">
-        <v>8.0062417258549239</v>
+        <v>2.2985858665641068</v>
       </c>
       <c r="AH6" s="0">
-        <v>9.7202783600427551</v>
+        <v>3.4056064178229928</v>
       </c>
       <c r="AI6" s="0">
         <v>0</v>
       </c>
       <c r="AJ6" s="0">
-        <v>0.25733073433374154</v>
+        <v>-0.033447675857234738</v>
       </c>
       <c r="AK6" s="0">
-        <v>0.19964024833462002</v>
+        <v>-0.081200175905313254</v>
       </c>
     </row>
     <row r="7">
@@ -945,7 +945,7 @@
         <v>28.399447404775955</v>
       </c>
       <c r="H7" s="0">
-        <v>27.689189804330326</v>
+        <v>28.399447404775955</v>
       </c>
       <c r="I7" s="0">
         <v>-9.3337573541103609</v>
@@ -954,7 +954,7 @@
         <v>-9.3337573541103609</v>
       </c>
       <c r="K7" s="0">
-        <v>-9.5161786582947485</v>
+        <v>-9.3337573541103609</v>
       </c>
       <c r="L7" s="0">
         <v>1.957335080270544</v>
@@ -963,7 +963,7 @@
         <v>1.957335080270544</v>
       </c>
       <c r="N7" s="0">
-        <v>1.9194434842835171</v>
+        <v>1.957335080270544</v>
       </c>
       <c r="O7" s="0">
         <v>1</v>
@@ -990,7 +990,7 @@
         <v>0</v>
       </c>
       <c r="W7" s="0">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X7" s="0">
         <v>100</v>
@@ -1002,10 +1002,10 @@
         <v>100</v>
       </c>
       <c r="AA7" s="0">
-        <v>99.799999999999997</v>
+        <v>100</v>
       </c>
       <c r="AB7" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC7" s="0">
         <v>0</v>
@@ -1014,7 +1014,7 @@
         <v>0</v>
       </c>
       <c r="AE7" s="0">
-        <v>-0.71025760044562958</v>
+        <v>0</v>
       </c>
       <c r="AF7" s="0">
         <v>0</v>
@@ -1023,7 +1023,7 @@
         <v>0</v>
       </c>
       <c r="AH7" s="0">
-        <v>-0.18242130418438807</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="0">
         <v>0</v>
@@ -1032,7 +1032,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="0">
-        <v>-0.03789159598702696</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1058,7 +1058,7 @@
         <v>35.106055948355184</v>
       </c>
       <c r="H8" s="0">
-        <v>33.555952506321304</v>
+        <v>35.521515738591972</v>
       </c>
       <c r="I8" s="0">
         <v>-12.746730083234258</v>
@@ -1067,7 +1067,7 @@
         <v>-12.746730083234258</v>
       </c>
       <c r="K8" s="0">
-        <v>-13.082199302736541</v>
+        <v>-12.478420680205382</v>
       </c>
       <c r="L8" s="0">
         <v>1.7924158170424755</v>
@@ -1076,7 +1076,7 @@
         <v>1.7924158170424755</v>
       </c>
       <c r="N8" s="0">
-        <v>1.7422277666827779</v>
+        <v>1.8275256756097</v>
       </c>
       <c r="O8" s="0">
         <v>1</v>
@@ -1103,7 +1103,7 @@
         <v>0</v>
       </c>
       <c r="W8" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X8" s="0">
         <v>100</v>
@@ -1115,10 +1115,10 @@
         <v>100</v>
       </c>
       <c r="AA8" s="0">
-        <v>99.603174603174608</v>
+        <v>99.702380952380949</v>
       </c>
       <c r="AB8" s="0">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AC8" s="0">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="AE8" s="0">
-        <v>-1.5501034420338788</v>
+        <v>0.41545979023678292</v>
       </c>
       <c r="AF8" s="0">
         <v>0</v>
@@ -1136,7 +1136,7 @@
         <v>0</v>
       </c>
       <c r="AH8" s="0">
-        <v>-0.33546921950228237</v>
+        <v>0.26830940302887685</v>
       </c>
       <c r="AI8" s="0">
         <v>0</v>
@@ -1145,7 +1145,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="0">
-        <v>-0.050188050359697645</v>
+        <v>0.035109858567224483</v>
       </c>
     </row>
     <row r="9">
@@ -1168,28 +1168,28 @@
         <v>21.387940841865927</v>
       </c>
       <c r="G9" s="0">
-        <v>19.898450918230147</v>
+        <v>17.931825365073738</v>
       </c>
       <c r="H9" s="0">
-        <v>20.875150582990077</v>
+        <v>20.895372796997979</v>
       </c>
       <c r="I9" s="0">
         <v>-22.253490637514915</v>
       </c>
       <c r="J9" s="0">
-        <v>-23.207478665404135</v>
+        <v>-24.467062368040249</v>
       </c>
       <c r="K9" s="0">
-        <v>-22.300702067618861</v>
+        <v>-22.836060242203594</v>
       </c>
       <c r="L9" s="0">
         <v>0.95343034850768338</v>
       </c>
       <c r="M9" s="0">
-        <v>0.92463872031323802</v>
+        <v>0.84401371670864311</v>
       </c>
       <c r="N9" s="0">
-        <v>0.977374703633624</v>
+        <v>0.97246256464239911</v>
       </c>
       <c r="O9" s="0">
         <v>1</v>
@@ -1216,7 +1216,7 @@
         <v>2</v>
       </c>
       <c r="W9" s="0">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X9" s="0">
         <v>100</v>
@@ -1228,37 +1228,37 @@
         <v>95.199999999999989</v>
       </c>
       <c r="AA9" s="0">
-        <v>94.299999999999997</v>
+        <v>94.199999999999989</v>
       </c>
       <c r="AB9" s="0">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AC9" s="0">
         <v>0</v>
       </c>
       <c r="AD9" s="0">
-        <v>-1.4894899236357784</v>
+        <v>-3.4561154767921876</v>
       </c>
       <c r="AE9" s="0">
-        <v>-0.51279025887585039</v>
+        <v>-0.49256804486794703</v>
       </c>
       <c r="AF9" s="0">
         <v>0</v>
       </c>
       <c r="AG9" s="0">
-        <v>-0.95398802788921877</v>
+        <v>-2.2135717305253322</v>
       </c>
       <c r="AH9" s="0">
-        <v>-0.047211430103943908</v>
+        <v>-0.58256960468867636</v>
       </c>
       <c r="AI9" s="0">
         <v>0</v>
       </c>
       <c r="AJ9" s="0">
-        <v>-0.028791628194445362</v>
+        <v>-0.10941663179904026</v>
       </c>
       <c r="AK9" s="0">
-        <v>0.02394435512594062</v>
+        <v>0.019032216134715729</v>
       </c>
     </row>
     <row r="10">
